--- a/salidas/empresas/MSFT.xlsx
+++ b/salidas/empresas/MSFT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>19.5047607421875</v>
+        <v>19.50475311279297</v>
       </c>
       <c r="C2" t="n">
         <v>28.14999961853027</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.68094635009766</v>
+        <v>18.68095397949219</v>
       </c>
       <c r="C3" t="n">
         <v>26.8700008392334</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>18.91733360290527</v>
+        <v>18.91732597351074</v>
       </c>
       <c r="C4" t="n">
         <v>27.20999908447266</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.7899169921875</v>
+        <v>16.78990936279297</v>
       </c>
       <c r="C5" t="n">
         <v>24.14999961853027</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.80846881866455</v>
+        <v>15.80846977233887</v>
       </c>
       <c r="C6" t="n">
         <v>22.64999961853027</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>16.26212882995605</v>
+        <v>16.26213073730469</v>
       </c>
       <c r="C7" t="n">
         <v>23.29999923706055</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>16.79256439208984</v>
+        <v>16.79256820678711</v>
       </c>
       <c r="C8" t="n">
         <v>24.05999946594238</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>18.00325202941895</v>
+        <v>18.00325584411621</v>
       </c>
       <c r="C9" t="n">
         <v>25.70000076293945</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.11179542541504</v>
+        <v>20.11180877685547</v>
       </c>
       <c r="C11" t="n">
         <v>28.70999908447266</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.63746070861816</v>
+        <v>20.6374626159668</v>
       </c>
       <c r="C12" t="n">
         <v>29.36000061035156</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.98891639709473</v>
+        <v>20.98891258239746</v>
       </c>
       <c r="C13" t="n">
         <v>29.86000061035156</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.69181060791016</v>
+        <v>21.69182395935059</v>
       </c>
       <c r="C14" t="n">
         <v>30.86000061035156</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.86965370178223</v>
+        <v>19.8696460723877</v>
       </c>
       <c r="C15" t="n">
         <v>28.17000007629395</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.65804862976074</v>
+        <v>19.65804481506348</v>
       </c>
       <c r="C16" t="n">
         <v>27.8700008392334</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.11811447143555</v>
+        <v>21.11811256408691</v>
       </c>
       <c r="C17" t="n">
         <v>29.94000053405762</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.71724319458008</v>
+        <v>21.71725273132324</v>
       </c>
       <c r="C18" t="n">
         <v>30.69000053405762</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>20.85392951965332</v>
+        <v>20.85393714904785</v>
       </c>
       <c r="C19" t="n">
         <v>29.46999931335449</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>20.5142707824707</v>
+        <v>20.51427459716797</v>
       </c>
       <c r="C20" t="n">
         <v>28.98999977111816</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>20.40155029296875</v>
+        <v>20.40154266357422</v>
       </c>
       <c r="C21" t="n">
         <v>28.72999954223633</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>20.91992950439453</v>
+        <v>20.91992568969727</v>
       </c>
       <c r="C22" t="n">
         <v>29.45999908447266</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>26.13926696777344</v>
+        <v>26.13926124572754</v>
       </c>
       <c r="C23" t="n">
         <v>36.81000137329102</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>23.93868064880371</v>
+        <v>23.93868446350098</v>
       </c>
       <c r="C24" t="n">
         <v>33.59999847412109</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.36361122131348</v>
+        <v>25.36360740661621</v>
       </c>
       <c r="C25" t="n">
         <v>35.59999847412109</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>23.22622299194336</v>
+        <v>23.22621917724609</v>
       </c>
       <c r="C26" t="n">
         <v>32.59999847412109</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>19.45423316955566</v>
+        <v>19.4542350769043</v>
       </c>
       <c r="C27" t="n">
         <v>27.20000076293945</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>20.29819679260254</v>
+        <v>20.29820442199707</v>
       </c>
       <c r="C28" t="n">
         <v>28.3799991607666</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>20.39833450317383</v>
+        <v>20.39833641052246</v>
       </c>
       <c r="C29" t="n">
         <v>28.52000045776367</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>20.32985496520996</v>
+        <v>20.32986068725586</v>
       </c>
       <c r="C30" t="n">
         <v>28.31999969482422</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>19.74839019775391</v>
+        <v>19.74839782714844</v>
       </c>
       <c r="C31" t="n">
         <v>27.51000022888184</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>18.46342086791992</v>
+        <v>18.46341514587402</v>
       </c>
       <c r="C32" t="n">
         <v>25.71999931335449</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>19.66859245300293</v>
+        <v>19.66860008239746</v>
       </c>
       <c r="C33" t="n">
         <v>27.29000091552734</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>16.09379196166992</v>
+        <v>16.09379386901855</v>
       </c>
       <c r="C35" t="n">
         <v>22.32999992370605</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.67178535461426</v>
+        <v>14.67178916931152</v>
       </c>
       <c r="C36" t="n">
         <v>20.21999931335449</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.10581874847412</v>
+        <v>14.10580825805664</v>
       </c>
       <c r="C37" t="n">
         <v>19.44000053405762</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.40789222717285</v>
+        <v>12.40789413452148</v>
       </c>
       <c r="C38" t="n">
         <v>17.10000038146973</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.79891204833984</v>
+        <v>11.79891586303711</v>
       </c>
       <c r="C39" t="n">
         <v>16.14999961853027</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.80160427093506</v>
+        <v>14.80161571502686</v>
       </c>
       <c r="C41" t="n">
         <v>20.26000022888184</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.35879707336426</v>
+        <v>15.35880565643311</v>
       </c>
       <c r="C42" t="n">
         <v>20.88999938964844</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.47624397277832</v>
+        <v>17.47624015808105</v>
       </c>
       <c r="C43" t="n">
         <v>23.77000045776367</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>18.22514533996582</v>
+        <v>18.22514152526855</v>
       </c>
       <c r="C45" t="n">
         <v>24.64999961853027</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,7 +1349,7 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1362,11 +1374,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.84059715270996</v>
+        <v>21.84059524536133</v>
       </c>
       <c r="C48" t="n">
         <v>29.40999984741211</v>
@@ -1387,11 +1399,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>22.63520240783691</v>
+        <v>22.63520622253418</v>
       </c>
       <c r="C49" t="n">
         <v>30.47999954223633</v>
@@ -1412,11 +1424,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.92716789245605</v>
+        <v>20.92716598510742</v>
       </c>
       <c r="C50" t="n">
         <v>28.18000030517578</v>
@@ -1437,11 +1449,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>21.3906192779541</v>
+        <v>21.39061546325684</v>
       </c>
       <c r="C51" t="n">
         <v>28.67000007629395</v>
@@ -1462,11 +1474,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.85320091247559</v>
+        <v>21.85320281982422</v>
       </c>
       <c r="C52" t="n">
         <v>29.29000091552734</v>
@@ -1487,11 +1499,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>22.78582191467285</v>
+        <v>22.78581809997559</v>
       </c>
       <c r="C53" t="n">
         <v>30.54000091552734</v>
@@ -1512,11 +1524,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>19.33617401123047</v>
+        <v>19.336181640625</v>
       </c>
       <c r="C54" t="n">
         <v>25.79999923706055</v>
@@ -1537,11 +1549,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>17.24516487121582</v>
+        <v>17.24517250061035</v>
       </c>
       <c r="C55" t="n">
         <v>23.01000022888184</v>
@@ -1562,11 +1574,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.34366798400879</v>
+        <v>19.34366989135742</v>
       </c>
       <c r="C56" t="n">
         <v>25.80999946594238</v>
@@ -1591,11 +1603,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.68374824523926</v>
+        <v>17.68376350402832</v>
       </c>
       <c r="C57" t="n">
         <v>23.46999931335449</v>
@@ -1620,11 +1632,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>18.45228958129883</v>
+        <v>18.45229339599609</v>
       </c>
       <c r="C58" t="n">
         <v>24.48999977111816</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.09483337402344</v>
+        <v>20.0948314666748</v>
       </c>
       <c r="C59" t="n">
         <v>26.67000007629395</v>
@@ -1678,7 +1690,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1707,11 +1719,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>21.1583366394043</v>
+        <v>21.1583423614502</v>
       </c>
       <c r="C61" t="n">
         <v>27.90999984741211</v>
@@ -1736,11 +1748,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>21.02188491821289</v>
+        <v>21.02188301086426</v>
       </c>
       <c r="C62" t="n">
         <v>27.72999954223633</v>
@@ -1765,11 +1777,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.26917839050293</v>
+        <v>20.2691764831543</v>
       </c>
       <c r="C63" t="n">
         <v>26.57999992370605</v>
@@ -1794,11 +1806,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.36171531677246</v>
+        <v>19.36172103881836</v>
       </c>
       <c r="C64" t="n">
         <v>25.38999938964844</v>
@@ -1823,11 +1835,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>19.76587867736816</v>
+        <v>19.76588249206543</v>
       </c>
       <c r="C65" t="n">
         <v>25.92000007629395</v>
@@ -1852,11 +1864,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>19.19694709777832</v>
+        <v>19.19694519042969</v>
       </c>
       <c r="C66" t="n">
         <v>25.01000022888184</v>
@@ -1881,11 +1893,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>19.95684432983398</v>
+        <v>19.95684623718262</v>
       </c>
       <c r="C67" t="n">
         <v>26</v>
@@ -1910,11 +1922,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.03144645690918</v>
+        <v>21.03143882751465</v>
       </c>
       <c r="C68" t="n">
         <v>27.39999961853027</v>
@@ -1939,11 +1951,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>20.5462532043457</v>
+        <v>20.54625511169434</v>
       </c>
       <c r="C69" t="n">
         <v>26.60000038146973</v>
@@ -1968,11 +1980,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>19.22542381286621</v>
+        <v>19.22541999816895</v>
       </c>
       <c r="C70" t="n">
         <v>24.88999938964844</v>
@@ -1997,7 +2009,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2026,11 +2038,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.90716743469238</v>
+        <v>19.90716934204102</v>
       </c>
       <c r="C72" t="n">
         <v>25.57999992370605</v>
@@ -2055,11 +2067,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.2028980255127</v>
+        <v>20.20289421081543</v>
       </c>
       <c r="C73" t="n">
         <v>25.95999908447266</v>
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2113,11 +2125,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.86369705200195</v>
+        <v>24.86369132995605</v>
       </c>
       <c r="C75" t="n">
         <v>31.73999977111816</v>
@@ -2142,11 +2154,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>25.27103805541992</v>
+        <v>25.27104187011719</v>
       </c>
       <c r="C76" t="n">
         <v>32.2599983215332</v>
@@ -2171,11 +2183,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>25.08303070068359</v>
+        <v>25.08303260803223</v>
       </c>
       <c r="C77" t="n">
         <v>32.02000045776367</v>
@@ -2200,11 +2212,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.01617431640625</v>
+        <v>23.01617813110352</v>
       </c>
       <c r="C78" t="n">
         <v>29.19000053405762</v>
@@ -2229,11 +2241,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>24.12006950378418</v>
+        <v>24.12007522583008</v>
       </c>
       <c r="C79" t="n">
         <v>30.59000015258789</v>
@@ -2258,11 +2270,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>23.2369499206543</v>
+        <v>23.23695182800293</v>
       </c>
       <c r="C80" t="n">
         <v>29.46999931335449</v>
@@ -2287,11 +2299,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>24.46240997314453</v>
+        <v>24.46241760253906</v>
       </c>
       <c r="C81" t="n">
         <v>30.81999969482422</v>
@@ -2316,7 +2328,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2345,11 +2357,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.65274047851562</v>
+        <v>22.65273666381836</v>
       </c>
       <c r="C83" t="n">
         <v>28.54000091552734</v>
@@ -2374,11 +2386,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>21.30242156982422</v>
+        <v>21.30241394042969</v>
       </c>
       <c r="C84" t="n">
         <v>26.6200008392334</v>
@@ -2403,7 +2415,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2432,11 +2444,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>21.96660804748535</v>
+        <v>21.96662330627441</v>
       </c>
       <c r="C86" t="n">
         <v>27.45000076293945</v>
@@ -2461,11 +2473,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>22.43088722229004</v>
+        <v>22.43088912963867</v>
       </c>
       <c r="C87" t="n">
         <v>27.79999923706055</v>
@@ -2490,11 +2502,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>23.08444786071777</v>
+        <v>23.08445167541504</v>
       </c>
       <c r="C88" t="n">
         <v>28.61000061035156</v>
@@ -2519,7 +2531,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2548,11 +2560,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>28.35710144042969</v>
+        <v>28.35710716247559</v>
       </c>
       <c r="C90" t="n">
         <v>34.90000152587891</v>
@@ -2577,11 +2589,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>28.06460189819336</v>
+        <v>28.06458473205566</v>
       </c>
       <c r="C91" t="n">
         <v>34.54000091552734</v>
@@ -2606,11 +2618,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>25.87078094482422</v>
+        <v>25.87077522277832</v>
       </c>
       <c r="C92" t="n">
         <v>31.84000015258789</v>
@@ -2635,11 +2647,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>27.32954978942871</v>
+        <v>27.32955360412598</v>
       </c>
       <c r="C93" t="n">
         <v>33.40000152587891</v>
@@ -2664,11 +2676,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.23136138916016</v>
+        <v>27.23135566711426</v>
       </c>
       <c r="C94" t="n">
         <v>33.27999877929688</v>
@@ -2693,11 +2705,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>28.97423362731934</v>
+        <v>28.97422790527344</v>
       </c>
       <c r="C95" t="n">
         <v>35.40999984741211</v>
@@ -2722,11 +2734,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.4365062713623</v>
+        <v>31.43649101257324</v>
       </c>
       <c r="C96" t="n">
         <v>38.13000106811523</v>
@@ -2751,11 +2763,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>30.84288597106934</v>
+        <v>30.8428840637207</v>
       </c>
       <c r="C97" t="n">
         <v>37.40999984741211</v>
@@ -2780,11 +2792,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>31.19738960266113</v>
+        <v>31.19741249084473</v>
       </c>
       <c r="C98" t="n">
         <v>37.84000015258789</v>
@@ -2809,11 +2821,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>31.82173728942871</v>
+        <v>31.82174301147461</v>
       </c>
       <c r="C99" t="n">
         <v>38.31000137329102</v>
@@ -2838,11 +2850,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.04784774780273</v>
+        <v>34.04784393310547</v>
       </c>
       <c r="C100" t="n">
         <v>40.9900016784668</v>
@@ -2867,11 +2879,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>33.55777359008789</v>
+        <v>33.55776214599609</v>
       </c>
       <c r="C101" t="n">
         <v>40.40000152587891</v>
@@ -2896,7 +2908,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2925,11 +2937,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>34.88196563720703</v>
+        <v>34.88195037841797</v>
       </c>
       <c r="C103" t="n">
         <v>41.70000076293945</v>
@@ -2954,11 +2966,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>36.10324096679688</v>
+        <v>36.10324478149414</v>
       </c>
       <c r="C104" t="n">
         <v>43.15999984741211</v>
@@ -2983,11 +2995,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>38.23944091796875</v>
+        <v>38.23944473266602</v>
       </c>
       <c r="C105" t="n">
         <v>45.43000030517578</v>
@@ -3012,11 +3024,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>39.02223587036133</v>
+        <v>39.02225494384766</v>
       </c>
       <c r="C106" t="n">
         <v>46.36000061035156</v>
@@ -3041,11 +3053,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.51886749267578</v>
+        <v>39.51885604858398</v>
       </c>
       <c r="C107" t="n">
         <v>46.95000076293945</v>
@@ -3070,7 +3082,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3099,7 +3111,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3128,7 +3140,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3157,11 +3169,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>37.40664672851562</v>
+        <v>37.40665435791016</v>
       </c>
       <c r="C111" t="n">
         <v>43.84999847412109</v>
@@ -3186,11 +3198,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>34.68539810180664</v>
+        <v>34.68539428710938</v>
       </c>
       <c r="C112" t="n">
         <v>40.65999984741211</v>
@@ -3215,11 +3227,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>41.4927978515625</v>
+        <v>41.49278259277344</v>
       </c>
       <c r="C113" t="n">
         <v>48.63999938964844</v>
@@ -3244,11 +3256,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>40.23413848876953</v>
+        <v>40.2341423034668</v>
       </c>
       <c r="C114" t="n">
         <v>46.86000061035156</v>
@@ -3273,11 +3285,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>37.90732574462891</v>
+        <v>37.90732955932617</v>
       </c>
       <c r="C115" t="n">
         <v>44.15000152587891</v>
@@ -3302,11 +3314,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>40.09676742553711</v>
+        <v>40.09676361083984</v>
       </c>
       <c r="C116" t="n">
         <v>46.70000076293945</v>
@@ -3331,11 +3343,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>37.61281585693359</v>
+        <v>37.61282348632812</v>
       </c>
       <c r="C117" t="n">
         <v>43.52000045776367</v>
@@ -3360,11 +3372,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>38.25238037109375</v>
+        <v>38.25237274169922</v>
       </c>
       <c r="C118" t="n">
         <v>44.2599983215332</v>
@@ -3389,11 +3401,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>45.49491882324219</v>
+        <v>45.49491500854492</v>
       </c>
       <c r="C119" t="n">
         <v>52.63999938964844</v>
@@ -3418,11 +3430,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>47.28942108154297</v>
+        <v>47.2894172668457</v>
       </c>
       <c r="C120" t="n">
         <v>54.34999847412109</v>
@@ -3447,11 +3459,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>48.27262878417969</v>
+        <v>48.27262496948242</v>
       </c>
       <c r="C121" t="n">
         <v>55.47999954223633</v>
@@ -3476,7 +3488,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3505,7 +3517,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3534,7 +3546,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3563,11 +3575,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>43.70295333862305</v>
+        <v>43.70296096801758</v>
       </c>
       <c r="C125" t="n">
         <v>49.86999893188477</v>
@@ -3592,11 +3604,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>46.7707633972168</v>
+        <v>46.77075958251953</v>
       </c>
       <c r="C126" t="n">
         <v>53</v>
@@ -3621,11 +3633,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>45.15584945678711</v>
+        <v>45.15583801269531</v>
       </c>
       <c r="C127" t="n">
         <v>51.16999816894531</v>
@@ -3650,11 +3662,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>50.01824569702148</v>
+        <v>50.01824188232422</v>
       </c>
       <c r="C128" t="n">
         <v>56.68000030517578</v>
@@ -3679,11 +3691,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>51.02260208129883</v>
+        <v>51.02260589599609</v>
       </c>
       <c r="C129" t="n">
         <v>57.45999908447266</v>
@@ -3708,11 +3720,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>51.14691925048828</v>
+        <v>51.14691543579102</v>
       </c>
       <c r="C130" t="n">
         <v>57.59999847412109</v>
@@ -3737,11 +3749,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>53.20699691772461</v>
+        <v>53.20698547363281</v>
       </c>
       <c r="C131" t="n">
         <v>59.91999816894531</v>
@@ -3766,11 +3778,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>53.87039566040039</v>
+        <v>53.87038803100586</v>
       </c>
       <c r="C132" t="n">
         <v>60.2599983215332</v>
@@ -3795,11 +3807,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>55.5510368347168</v>
+        <v>55.55105209350586</v>
       </c>
       <c r="C133" t="n">
         <v>62.13999938964844</v>
@@ -3824,11 +3836,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>57.79489898681641</v>
+        <v>57.79491424560547</v>
       </c>
       <c r="C134" t="n">
         <v>64.65000152587891</v>
@@ -3853,11 +3865,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>57.54269027709961</v>
+        <v>57.54269790649414</v>
       </c>
       <c r="C135" t="n">
         <v>63.97999954223633</v>
@@ -3882,11 +3894,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>59.2335319519043</v>
+        <v>59.23354339599609</v>
       </c>
       <c r="C136" t="n">
         <v>65.86000061035156</v>
@@ -3911,11 +3923,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>61.57193756103516</v>
+        <v>61.57194137573242</v>
       </c>
       <c r="C137" t="n">
         <v>68.45999908447266</v>
@@ -3940,11 +3952,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>63.17312240600586</v>
+        <v>63.17315292358398</v>
       </c>
       <c r="C138" t="n">
         <v>69.83999633789062</v>
@@ -3969,11 +3981,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>62.34999847412109</v>
+        <v>62.35000228881836</v>
       </c>
       <c r="C139" t="n">
         <v>68.93000030517578</v>
@@ -3998,11 +4010,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.76010131835938</v>
+        <v>65.76013946533203</v>
       </c>
       <c r="C140" t="n">
         <v>72.69999694824219</v>
@@ -4027,11 +4039,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>67.99284362792969</v>
+        <v>67.99287414550781</v>
       </c>
       <c r="C141" t="n">
         <v>74.76999664306641</v>
@@ -4056,11 +4068,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>67.73823547363281</v>
+        <v>67.73822784423828</v>
       </c>
       <c r="C142" t="n">
         <v>74.48999786376953</v>
@@ -4085,11 +4097,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>75.64055633544922</v>
+        <v>75.64060211181641</v>
       </c>
       <c r="C143" t="n">
         <v>83.18000030517578</v>
@@ -4114,7 +4126,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4143,11 +4155,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.17732238769531</v>
+        <v>78.17733001708984</v>
       </c>
       <c r="C145" t="n">
         <v>85.54000091552734</v>
@@ -4172,11 +4184,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>86.83222961425781</v>
+        <v>86.83221435546875</v>
       </c>
       <c r="C146" t="n">
         <v>95.01000213623047</v>
@@ -4201,11 +4213,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>86.10151672363281</v>
+        <v>86.10150909423828</v>
       </c>
       <c r="C147" t="n">
         <v>93.76999664306641</v>
@@ -4230,11 +4242,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>83.80597686767578</v>
+        <v>83.80596160888672</v>
       </c>
       <c r="C148" t="n">
         <v>91.26999664306641</v>
@@ -4259,11 +4271,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>85.87195587158203</v>
+        <v>85.87193298339844</v>
       </c>
       <c r="C149" t="n">
         <v>93.51999664306641</v>
@@ -4288,11 +4300,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>91.15024566650391</v>
+        <v>91.15026092529297</v>
       </c>
       <c r="C150" t="n">
         <v>98.83999633789062</v>
@@ -4317,11 +4329,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>90.93814849853516</v>
+        <v>90.93815612792969</v>
       </c>
       <c r="C151" t="n">
         <v>98.61000061035156</v>
@@ -4346,11 +4358,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>97.82696533203125</v>
+        <v>97.82698822021484</v>
       </c>
       <c r="C152" t="n">
         <v>106.0800018310547</v>
@@ -4375,11 +4387,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>103.9893951416016</v>
+        <v>103.989387512207</v>
       </c>
       <c r="C153" t="n">
         <v>112.3300018310547</v>
@@ -4404,11 +4416,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>105.8778991699219</v>
+        <v>105.8779067993164</v>
       </c>
       <c r="C154" t="n">
         <v>114.370002746582</v>
@@ -4433,11 +4445,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>98.87924194335938</v>
+        <v>98.87923431396484</v>
       </c>
       <c r="C155" t="n">
         <v>106.8099975585938</v>
@@ -4462,11 +4474,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>103.0998001098633</v>
+        <v>103.0997848510742</v>
       </c>
       <c r="C156" t="n">
         <v>110.8899993896484</v>
@@ -4491,11 +4503,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>94.43456268310547</v>
+        <v>94.43452453613281</v>
       </c>
       <c r="C157" t="n">
         <v>101.5699996948242</v>
@@ -4520,7 +4532,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4549,11 +4561,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>104.6045379638672</v>
+        <v>104.6045303344727</v>
       </c>
       <c r="C159" t="n">
         <v>112.0299987792969</v>
@@ -4578,11 +4590,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>110.122802734375</v>
+        <v>110.1228332519531</v>
       </c>
       <c r="C160" t="n">
         <v>117.9400024414062</v>
@@ -4607,11 +4619,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>121.9437255859375</v>
+        <v>121.9436950683594</v>
       </c>
       <c r="C161" t="n">
         <v>130.6000061035156</v>
@@ -4636,7 +4648,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4665,11 +4677,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>125.5439758300781</v>
+        <v>125.5440063476562</v>
       </c>
       <c r="C163" t="n">
         <v>133.9600067138672</v>
@@ -4694,11 +4706,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>127.7089080810547</v>
+        <v>127.7088775634766</v>
       </c>
       <c r="C164" t="n">
         <v>136.2700042724609</v>
@@ -4723,11 +4735,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>129.6292114257812</v>
+        <v>129.6292266845703</v>
       </c>
       <c r="C165" t="n">
         <v>137.8600006103516</v>
@@ -4752,11 +4764,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>130.7293853759766</v>
+        <v>130.7293548583984</v>
       </c>
       <c r="C166" t="n">
         <v>139.0299987792969</v>
@@ -4781,11 +4793,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>134.8102416992188</v>
+        <v>134.8102111816406</v>
       </c>
       <c r="C167" t="n">
         <v>143.3699951171875</v>
@@ -4810,11 +4822,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>142.8263854980469</v>
+        <v>142.8263702392578</v>
       </c>
       <c r="C168" t="n">
         <v>151.3800048828125</v>
@@ -4839,7 +4851,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4868,11 +4880,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>160.6112976074219</v>
+        <v>160.6112365722656</v>
       </c>
       <c r="C170" t="n">
         <v>170.2299957275391</v>
@@ -4897,11 +4909,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>153.2732391357422</v>
+        <v>153.2732543945312</v>
       </c>
       <c r="C171" t="n">
         <v>162.0099945068359</v>
@@ -4926,11 +4938,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>149.2051391601562</v>
+        <v>149.2051239013672</v>
       </c>
       <c r="C172" t="n">
         <v>157.7100067138672</v>
@@ -4955,11 +4967,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>169.5456695556641</v>
+        <v>169.5457153320312</v>
       </c>
       <c r="C173" t="n">
         <v>179.2100067138672</v>
@@ -4984,7 +4996,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5013,7 +5025,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5042,11 +5054,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>194.4945220947266</v>
+        <v>194.4945373535156</v>
       </c>
       <c r="C176" t="n">
         <v>205.0099945068359</v>
@@ -5071,11 +5083,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>214.4792327880859</v>
+        <v>214.4792022705078</v>
       </c>
       <c r="C177" t="n">
         <v>225.5299987792969</v>
@@ -5100,11 +5112,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>200.0239868164062</v>
+        <v>200.0240020751953</v>
       </c>
       <c r="C178" t="n">
         <v>210.3300018310547</v>
@@ -5129,11 +5141,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>192.5491180419922</v>
+        <v>192.5491638183594</v>
       </c>
       <c r="C179" t="n">
         <v>202.4700012207031</v>
@@ -5158,11 +5170,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>204.11376953125</v>
+        <v>204.1137237548828</v>
       </c>
       <c r="C180" t="n">
         <v>214.0700073242188</v>
@@ -5187,11 +5199,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>212.0754089355469</v>
+        <v>212.0753784179688</v>
       </c>
       <c r="C181" t="n">
         <v>222.4199981689453</v>
@@ -5216,11 +5228,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>221.1717071533203</v>
+        <v>221.1716766357422</v>
       </c>
       <c r="C182" t="n">
         <v>231.9600067138672</v>
@@ -5245,7 +5257,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5274,11 +5286,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>225.322265625</v>
+        <v>225.3222503662109</v>
       </c>
       <c r="C184" t="n">
         <v>235.7700042724609</v>
@@ -5303,7 +5315,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5332,11 +5344,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>239.1668243408203</v>
+        <v>239.1668395996094</v>
       </c>
       <c r="C186" t="n">
         <v>249.6799926757812</v>
@@ -5361,11 +5373,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>259.4933471679688</v>
+        <v>259.4933776855469</v>
       </c>
       <c r="C187" t="n">
         <v>270.8999938964844</v>
@@ -5390,11 +5402,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>272.9134826660156</v>
+        <v>272.9133911132812</v>
       </c>
       <c r="C188" t="n">
         <v>284.9100036621094</v>
@@ -5419,7 +5431,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5448,11 +5460,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>270.5662841796875</v>
+        <v>270.5663146972656</v>
       </c>
       <c r="C190" t="n">
         <v>281.9200134277344</v>
@@ -5477,11 +5489,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>318.2647705078125</v>
+        <v>318.2647399902344</v>
       </c>
       <c r="C191" t="n">
         <v>331.6199951171875</v>
@@ -5506,7 +5518,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5535,7 +5547,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5564,11 +5576,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>299.0020141601562</v>
+        <v>299.0019836425781</v>
       </c>
       <c r="C194" t="n">
         <v>310.9800109863281</v>
@@ -5593,11 +5605,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>287.8755798339844</v>
+        <v>287.8756103515625</v>
       </c>
       <c r="C195" t="n">
         <v>298.7900085449219</v>
@@ -5622,7 +5634,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5651,11 +5663,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>267.3825073242188</v>
+        <v>267.3824768066406</v>
       </c>
       <c r="C197" t="n">
         <v>277.5199890136719</v>
@@ -5680,11 +5692,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>262.5490112304688</v>
+        <v>262.5489807128906</v>
       </c>
       <c r="C198" t="n">
         <v>271.8699951171875</v>
@@ -5709,11 +5721,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>248.0246124267578</v>
+        <v>248.0245971679688</v>
       </c>
       <c r="C199" t="n">
         <v>256.8299865722656</v>
@@ -5738,7 +5750,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5767,11 +5779,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>253.0415191650391</v>
+        <v>253.0414886474609</v>
       </c>
       <c r="C201" t="n">
         <v>261.4700012207031</v>
@@ -5796,11 +5808,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>225.3924713134766</v>
+        <v>225.3924560546875</v>
       </c>
       <c r="C202" t="n">
         <v>232.8999938964844</v>
@@ -5825,11 +5837,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>224.6473083496094</v>
+        <v>224.6473236083984</v>
       </c>
       <c r="C203" t="n">
         <v>232.1300048828125</v>
@@ -5854,7 +5866,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5883,11 +5895,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>232.7434539794922</v>
+        <v>232.7434844970703</v>
       </c>
       <c r="C205" t="n">
         <v>239.8200073242188</v>
@@ -5912,11 +5924,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>240.4976959228516</v>
+        <v>240.4977111816406</v>
       </c>
       <c r="C206" t="n">
         <v>247.8099975585938</v>
@@ -5941,11 +5953,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>242.6664733886719</v>
+        <v>242.6664886474609</v>
       </c>
       <c r="C207" t="n">
         <v>249.4199981689453</v>
@@ -5970,11 +5982,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>280.4937133789062</v>
+        <v>280.49365234375</v>
       </c>
       <c r="C208" t="n">
         <v>288.2999877929688</v>
@@ -5999,11 +6011,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>298.9403991699219</v>
+        <v>298.9403686523438</v>
       </c>
       <c r="C209" t="n">
         <v>307.260009765625</v>
@@ -6028,11 +6040,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>320.1966857910156</v>
+        <v>320.1967163085938</v>
       </c>
       <c r="C210" t="n">
         <v>328.3900146484375</v>
@@ -6057,11 +6069,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>332.0435791015625</v>
+        <v>332.0435180664062</v>
       </c>
       <c r="C211" t="n">
         <v>340.5400085449219</v>
@@ -6086,11 +6098,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>327.538818359375</v>
+        <v>327.5387878417969</v>
       </c>
       <c r="C212" t="n">
         <v>335.9200134277344</v>
@@ -6115,11 +6127,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>320.2590026855469</v>
+        <v>320.259033203125</v>
       </c>
       <c r="C213" t="n">
         <v>327.760009765625</v>
@@ -6144,11 +6156,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>308.5238647460938</v>
+        <v>308.5238952636719</v>
       </c>
       <c r="C214" t="n">
         <v>315.75</v>
@@ -6173,11 +6185,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>330.3721923828125</v>
+        <v>330.3721618652344</v>
       </c>
       <c r="C215" t="n">
         <v>338.1099853515625</v>
@@ -6202,11 +6214,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>370.9899597167969</v>
+        <v>370.9898986816406</v>
       </c>
       <c r="C216" t="n">
         <v>378.9100036621094</v>
@@ -6231,11 +6243,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>368.1798706054688</v>
+        <v>368.1798400878906</v>
       </c>
       <c r="C217" t="n">
         <v>376.0400085449219</v>
@@ -6260,7 +6272,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6289,7 +6301,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6318,7 +6330,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6347,11 +6359,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>381.89697265625</v>
+        <v>381.8969421386719</v>
       </c>
       <c r="C221" t="n">
         <v>389.3299865722656</v>
@@ -6376,11 +6388,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>407.9389038085938</v>
+        <v>407.9389343261719</v>
       </c>
       <c r="C222" t="n">
         <v>415.1300048828125</v>
@@ -6405,11 +6417,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>439.2077331542969</v>
+        <v>439.2077026367188</v>
       </c>
       <c r="C223" t="n">
         <v>446.9500122070312</v>
@@ -6434,11 +6446,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>411.1031494140625</v>
+        <v>411.1031799316406</v>
       </c>
       <c r="C224" t="n">
         <v>418.3500061035156</v>
@@ -6463,11 +6475,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>410.6529846191406</v>
+        <v>410.6528930664062</v>
       </c>
       <c r="C225" t="n">
         <v>417.1400146484375</v>
@@ -6492,11 +6504,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>423.6082763671875</v>
+        <v>423.6082458496094</v>
       </c>
       <c r="C226" t="n">
         <v>430.2999877929688</v>
@@ -6521,11 +6533,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>400.0307006835938</v>
+        <v>400.0307312011719</v>
       </c>
       <c r="C227" t="n">
         <v>406.3500061035156</v>
@@ -6550,11 +6562,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>417.7090759277344</v>
+        <v>417.7090148925781</v>
       </c>
       <c r="C228" t="n">
         <v>423.4599914550781</v>
@@ -6579,11 +6591,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>415.7756958007812</v>
+        <v>415.7757263183594</v>
       </c>
       <c r="C229" t="n">
         <v>421.5</v>
@@ -6608,11 +6620,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>409.4231262207031</v>
+        <v>409.4231872558594</v>
       </c>
       <c r="C230" t="n">
         <v>415.0599975585938</v>
@@ -6637,7 +6649,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6666,11 +6678,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>371.0343933105469</v>
+        <v>371.034423828125</v>
       </c>
       <c r="C232" t="n">
         <v>375.3900146484375</v>
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6724,7 +6736,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6753,11 +6765,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>492.5411987304688</v>
+        <v>492.5411376953125</v>
       </c>
       <c r="C235" t="n">
         <v>497.4100036621094</v>
@@ -6782,7 +6794,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6811,11 +6823,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>502.5551147460938</v>
+        <v>502.5551452636719</v>
       </c>
       <c r="C237" t="n">
         <v>506.6900024414062</v>
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6869,11 +6881,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>513.5843505859375</v>
+        <v>513.5844116210938</v>
       </c>
       <c r="C239" t="n">
         <v>517.8099975585938</v>
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6927,11 +6939,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>480.5711364746094</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="C241" t="n">
         <v>483.6199951171875</v>
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7014,7 +7026,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7043,7 +7055,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7072,7 +7084,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7130,7 +7142,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7159,7 +7171,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7188,32 +7200,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>500.5899963378906</v>
+        <v>497.9299926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>500.5899963378906</v>
+        <v>497.9299926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>324980800</v>
+        <v>341648100</v>
       </c>
       <c r="E250" t="n">
         <v>17.95</v>
       </c>
       <c r="F250" t="n">
-        <v>27.88802208010533</v>
+        <v>27.73983246104631</v>
       </c>
       <c r="G250" t="n">
         <v>7425545491</v>
       </c>
       <c r="H250" t="n">
-        <v>3717153790146.53</v>
+        <v>3697401811947.311</v>
       </c>
       <c r="I250" t="n">
-        <v>0.04376524262007245</v>
+        <v>0.04600983192603001</v>
       </c>
     </row>
   </sheetData>
@@ -7245,75 +7257,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39264</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39355</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7349,13 +7361,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39356</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39447</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7391,13 +7403,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39448</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7433,13 +7445,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7466,7 +7478,7 @@
       <c r="I5" t="n">
         <v>1.88</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K5" t="n">
@@ -7479,13 +7491,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7512,7 +7524,7 @@
       <c r="I6" t="n">
         <v>1.91</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K6" t="n">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40206</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7558,7 +7570,7 @@
       <c r="I7" t="n">
         <v>1.88</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K7" t="n">
@@ -7571,13 +7583,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7604,7 +7616,7 @@
       <c r="I8" t="n">
         <v>1.74</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K8" t="n">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I9" t="n">
         <v>1.62</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K9" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I10" t="n">
         <v>1.54</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K10" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40206</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I11" t="n">
         <v>1.81</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K11" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I12" t="n">
         <v>1.93</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K12" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I13" t="n">
         <v>2.1</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K13" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I14" t="n">
         <v>2.32</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="K14" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I15" t="n">
         <v>2.35</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="K15" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I16" t="n">
         <v>2.51</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="K16" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I17" t="n">
         <v>2.69</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K17" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>40836</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I18" t="n">
         <v>2.75</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>40836</v>
       </c>
       <c r="K18" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I19" t="n">
         <v>2.76</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="K19" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I20" t="n">
         <v>2.75</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="K20" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K21" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I22" t="n">
         <v>1.85</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="K22" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41298</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I23" t="n">
         <v>1.83</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41298</v>
       </c>
       <c r="K23" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I24" t="n">
         <v>1.95</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="K24" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41485</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I25" t="n">
         <v>2.6</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41485</v>
       </c>
       <c r="K25" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I26" t="n">
         <v>2.69</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="K26" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41662</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I27" t="n">
         <v>2.71</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41662</v>
       </c>
       <c r="K27" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I28" t="n">
         <v>2.67</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K28" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I29" t="n">
         <v>2.63</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K29" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I30" t="n">
         <v>2.55</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K30" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42030</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I31" t="n">
         <v>2.48</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42030</v>
       </c>
       <c r="K31" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I32" t="n">
         <v>2.41</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K32" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I33" t="n">
         <v>1.46</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="K33" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I34" t="n">
         <v>1.49</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="K34" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I35" t="n">
         <v>1.4</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="K35" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I36" t="n">
         <v>1.26</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="K36" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I37" t="n">
         <v>2.05</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K37" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I38" t="n">
         <v>2.08</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="K38" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I39" t="n">
         <v>2.12</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="K39" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I40" t="n">
         <v>2.26</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K40" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I41" t="n">
         <v>2.7</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="K41" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I42" t="n">
         <v>2.94</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K42" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I43" t="n">
         <v>1.46</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="K43" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I44" t="n">
         <v>1.8</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K44" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I45" t="n">
         <v>2.11</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K45" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I46" t="n">
         <v>2.41</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K46" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I47" t="n">
         <v>4.31</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="K47" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I48" t="n">
         <v>4.5</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K48" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I49" t="n">
         <v>5.07</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K49" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I50" t="n">
         <v>5.31</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="K50" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I51" t="n">
         <v>5.74</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="K51" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I52" t="n">
         <v>5.999999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="K52" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I53" t="n">
         <v>5.749999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K53" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I54" t="n">
         <v>6.19</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="K54" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44222</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I55" t="n">
         <v>6.709999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44222</v>
       </c>
       <c r="K55" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I56" t="n">
         <v>7.34</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K56" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I57" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K57" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I58" t="n">
         <v>8.940000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="K58" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44586</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I59" t="n">
         <v>9.390000000000002</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44586</v>
       </c>
       <c r="K59" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I60" t="n">
         <v>9.580000000000002</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="K60" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I61" t="n">
         <v>9.65</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K61" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I62" t="n">
         <v>9.290000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K62" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>44950</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I63" t="n">
         <v>9.01</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>44950</v>
       </c>
       <c r="K63" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I64" t="n">
         <v>9.24</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K64" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I65" t="n">
         <v>9.68</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K65" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I66" t="n">
         <v>10.32</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K66" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I67" t="n">
         <v>11.05</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="K67" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I68" t="n">
         <v>11.54</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K68" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I69" t="n">
         <v>11.8</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K69" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10456,7 +10468,7 @@
       <c r="I70" t="n">
         <v>12.11</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K70" t="n">
@@ -10469,13 +10481,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10502,7 +10514,7 @@
       <c r="I71" t="n">
         <v>12.41</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="K71" t="n">
@@ -10515,13 +10527,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10548,7 +10560,7 @@
       <c r="I72" t="n">
         <v>12.93</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K72" t="n">
@@ -10561,13 +10573,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10594,7 +10606,7 @@
       <c r="I73" t="n">
         <v>13.64</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="K73" t="n">
@@ -10607,13 +10619,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10640,7 +10652,7 @@
       <c r="I74" t="n">
         <v>14.06</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="K74" t="n">
@@ -10653,13 +10665,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10686,7 +10698,7 @@
       <c r="I75" t="n">
         <v>15.99</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="K75" t="n">
@@ -10699,13 +10711,13 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="C76" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -10732,7 +10744,7 @@
       <c r="I76" t="n">
         <v>16.8</v>
       </c>
-      <c r="J76" s="1" t="n">
+      <c r="J76" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K76" t="n">
@@ -10745,13 +10757,13 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C77" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -10778,7 +10790,7 @@
       <c r="I77" t="n">
         <v>17.95</v>
       </c>
-      <c r="J77" s="1" t="n">
+      <c r="J77" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="K77" t="n">
@@ -10815,52 +10827,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40105</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="C2" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40203</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40206</v>
       </c>
       <c r="C3" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40287</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="C4" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40379</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="C5" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40473</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="C6" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40564</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40570</v>
       </c>
       <c r="C7" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40654</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="C8" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40744</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C9" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40833</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40836</v>
       </c>
       <c r="C10" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40925</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40935</v>
       </c>
       <c r="C11" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41016</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="C12" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41108</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C13" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41197</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="C14" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41292</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41298</v>
       </c>
       <c r="C15" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41375</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="C16" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41473</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41485</v>
       </c>
       <c r="C17" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41563</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="C18" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41656</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41662</v>
       </c>
       <c r="C19" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41746</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C20" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41842</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C21" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41928</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C22" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42026</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42030</v>
       </c>
       <c r="C23" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42110</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C24" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="C25" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42292</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="C26" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42391</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42397</v>
       </c>
       <c r="C27" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="C28" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42576</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C29" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42657</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="C30" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42755</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="C31" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C32" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42949</v>
       </c>
       <c r="C33" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C34" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43126</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="C35" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C36" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C37" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C38" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43490</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43495</v>
       </c>
       <c r="C39" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C40" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C41" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43761</v>
       </c>
       <c r="C42" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43854</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43859</v>
       </c>
       <c r="C43" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43950</v>
       </c>
       <c r="C44" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C45" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44126</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44131</v>
       </c>
       <c r="C46" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44217</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44222</v>
       </c>
       <c r="C47" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C48" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44403</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C49" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44495</v>
       </c>
       <c r="C50" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44581</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44586</v>
       </c>
       <c r="C51" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44672</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44677</v>
       </c>
       <c r="C52" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44767</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C53" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44854</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C54" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44945</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44950</v>
       </c>
       <c r="C55" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C56" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C57" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45218</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C58" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45316</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="C59" t="n">
@@ -12713,10 +12725,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45404</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C60" t="n">
@@ -12745,10 +12757,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45498</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C61" t="n">
@@ -12777,10 +12789,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45589</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C62" t="n">
@@ -12809,10 +12821,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45680</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="C63" t="n">
@@ -12841,10 +12853,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45771</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C64" t="n">
@@ -12873,10 +12885,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45862</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="C65" t="n">
@@ -12905,10 +12917,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45953</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C66" t="n">
@@ -12937,10 +12949,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46044</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46050</v>
       </c>
       <c r="C67" t="n">
@@ -12969,10 +12981,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46135</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C68" t="n">
@@ -13001,10 +13013,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46226</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="C69" t="n">
@@ -13051,12 +13063,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MSFT.xlsx
+++ b/salidas/empresas/MSFT.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>19.50475311279297</v>
+        <v>19.50475120544434</v>
       </c>
       <c r="C2" t="n">
         <v>28.14999961853027</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.68095397949219</v>
+        <v>18.68094825744629</v>
       </c>
       <c r="C3" t="n">
         <v>26.8700008392334</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>18.91732597351074</v>
+        <v>18.91732788085938</v>
       </c>
       <c r="C4" t="n">
         <v>27.20999908447266</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.78990936279297</v>
+        <v>16.78990745544434</v>
       </c>
       <c r="C5" t="n">
         <v>24.14999961853027</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.80846977233887</v>
+        <v>15.8084602355957</v>
       </c>
       <c r="C6" t="n">
         <v>22.64999961853027</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>16.79256820678711</v>
+        <v>16.79256439208984</v>
       </c>
       <c r="C8" t="n">
         <v>24.05999946594238</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.11180877685547</v>
+        <v>20.11180114746094</v>
       </c>
       <c r="C11" t="n">
         <v>28.70999908447266</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.6374626159668</v>
+        <v>20.6374568939209</v>
       </c>
       <c r="C12" t="n">
         <v>29.36000061035156</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.98891258239746</v>
+        <v>20.9889087677002</v>
       </c>
       <c r="C13" t="n">
         <v>29.86000061035156</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.69182395935059</v>
+        <v>21.69181442260742</v>
       </c>
       <c r="C14" t="n">
         <v>30.86000061035156</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.8696460723877</v>
+        <v>19.86965179443359</v>
       </c>
       <c r="C15" t="n">
         <v>28.17000007629395</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.65804481506348</v>
+        <v>19.65805244445801</v>
       </c>
       <c r="C16" t="n">
         <v>27.8700008392334</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.11811256408691</v>
+        <v>21.11810684204102</v>
       </c>
       <c r="C17" t="n">
         <v>29.94000053405762</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.71725273132324</v>
+        <v>21.71724700927734</v>
       </c>
       <c r="C18" t="n">
         <v>30.69000053405762</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>20.85393714904785</v>
+        <v>20.85393142700195</v>
       </c>
       <c r="C19" t="n">
         <v>29.46999931335449</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>20.51427459716797</v>
+        <v>20.5142707824707</v>
       </c>
       <c r="C20" t="n">
         <v>28.98999977111816</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>20.40154266357422</v>
+        <v>20.40154838562012</v>
       </c>
       <c r="C21" t="n">
         <v>28.72999954223633</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>20.91992568969727</v>
+        <v>20.91992950439453</v>
       </c>
       <c r="C22" t="n">
         <v>29.45999908447266</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>23.93868446350098</v>
+        <v>23.93868637084961</v>
       </c>
       <c r="C24" t="n">
         <v>33.59999847412109</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.36360740661621</v>
+        <v>25.36360168457031</v>
       </c>
       <c r="C25" t="n">
         <v>35.59999847412109</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>23.22621917724609</v>
+        <v>23.22622680664062</v>
       </c>
       <c r="C26" t="n">
         <v>32.59999847412109</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>19.4542350769043</v>
+        <v>19.45422744750977</v>
       </c>
       <c r="C27" t="n">
         <v>27.20000076293945</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>20.29820442199707</v>
+        <v>20.29821014404297</v>
       </c>
       <c r="C28" t="n">
         <v>28.3799991607666</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>20.32986068725586</v>
+        <v>20.32985877990723</v>
       </c>
       <c r="C30" t="n">
         <v>28.31999969482422</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>19.74839782714844</v>
+        <v>19.74839210510254</v>
       </c>
       <c r="C31" t="n">
         <v>27.51000022888184</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>18.46341514587402</v>
+        <v>18.46341896057129</v>
       </c>
       <c r="C32" t="n">
         <v>25.71999931335449</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>19.66860008239746</v>
+        <v>19.6685962677002</v>
       </c>
       <c r="C33" t="n">
         <v>27.29000091552734</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>19.23616409301758</v>
+        <v>19.23615837097168</v>
       </c>
       <c r="C34" t="n">
         <v>26.69000053405762</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>16.09379386901855</v>
+        <v>16.09379959106445</v>
       </c>
       <c r="C35" t="n">
         <v>22.32999992370605</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.67178916931152</v>
+        <v>14.67178440093994</v>
       </c>
       <c r="C36" t="n">
         <v>20.21999931335449</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.10580825805664</v>
+        <v>14.10581111907959</v>
       </c>
       <c r="C37" t="n">
         <v>19.44000053405762</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.40789413452148</v>
+        <v>12.40789222717285</v>
       </c>
       <c r="C38" t="n">
         <v>17.10000038146973</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>13.42081165313721</v>
+        <v>13.42081069946289</v>
       </c>
       <c r="C40" t="n">
         <v>18.3700008392334</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>14.80161571502686</v>
+        <v>14.80161285400391</v>
       </c>
       <c r="C41" t="n">
         <v>20.26000022888184</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.35880565643311</v>
+        <v>15.35880661010742</v>
       </c>
       <c r="C42" t="n">
         <v>20.88999938964844</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.47624015808105</v>
+        <v>17.47623825073242</v>
       </c>
       <c r="C43" t="n">
         <v>23.77000045776367</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.29243659973145</v>
+        <v>17.29244232177734</v>
       </c>
       <c r="C44" t="n">
         <v>23.52000045776367</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>18.22514152526855</v>
+        <v>18.22514533996582</v>
       </c>
       <c r="C45" t="n">
         <v>24.64999961853027</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>19.0162525177002</v>
+        <v>19.01625061035156</v>
       </c>
       <c r="C46" t="n">
         <v>25.71999931335449</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>20.50236129760742</v>
+        <v>20.50235748291016</v>
       </c>
       <c r="C47" t="n">
         <v>27.72999954223633</v>
@@ -1403,7 +1403,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>22.63520622253418</v>
+        <v>22.63520431518555</v>
       </c>
       <c r="C49" t="n">
         <v>30.47999954223633</v>
@@ -1428,7 +1428,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.92716598510742</v>
+        <v>20.92717361450195</v>
       </c>
       <c r="C50" t="n">
         <v>28.18000030517578</v>
@@ -1453,7 +1453,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>21.39061546325684</v>
+        <v>21.39062690734863</v>
       </c>
       <c r="C51" t="n">
         <v>28.67000007629395</v>
@@ -1478,7 +1478,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.85320281982422</v>
+        <v>21.85319328308105</v>
       </c>
       <c r="C52" t="n">
         <v>29.29000091552734</v>
@@ -1503,7 +1503,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>22.78581809997559</v>
+        <v>22.78582000732422</v>
       </c>
       <c r="C53" t="n">
         <v>30.54000091552734</v>
@@ -1528,7 +1528,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>19.336181640625</v>
+        <v>19.33617782592773</v>
       </c>
       <c r="C54" t="n">
         <v>25.79999923706055</v>
@@ -1553,7 +1553,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>17.24517250061035</v>
+        <v>17.24517440795898</v>
       </c>
       <c r="C55" t="n">
         <v>23.01000022888184</v>
@@ -1578,7 +1578,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.34366989135742</v>
+        <v>19.34366607666016</v>
       </c>
       <c r="C56" t="n">
         <v>25.80999946594238</v>
@@ -1607,7 +1607,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.68376350402832</v>
+        <v>17.68375587463379</v>
       </c>
       <c r="C57" t="n">
         <v>23.46999931335449</v>
@@ -1636,7 +1636,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>18.45229339599609</v>
+        <v>18.45228576660156</v>
       </c>
       <c r="C58" t="n">
         <v>24.48999977111816</v>
@@ -1694,7 +1694,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.14939308166504</v>
+        <v>19.14939117431641</v>
       </c>
       <c r="C60" t="n">
         <v>25.26000022888184</v>
@@ -1752,7 +1752,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>21.02188301086426</v>
+        <v>21.02188682556152</v>
       </c>
       <c r="C62" t="n">
         <v>27.72999954223633</v>
@@ -1781,7 +1781,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.2691764831543</v>
+        <v>20.26918029785156</v>
       </c>
       <c r="C63" t="n">
         <v>26.57999992370605</v>
@@ -1810,7 +1810,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.36172103881836</v>
+        <v>19.36171913146973</v>
       </c>
       <c r="C64" t="n">
         <v>25.38999938964844</v>
@@ -1839,7 +1839,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>19.76588249206543</v>
+        <v>19.76587677001953</v>
       </c>
       <c r="C65" t="n">
         <v>25.92000007629395</v>
@@ -1868,7 +1868,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>19.19694519042969</v>
+        <v>19.19694709777832</v>
       </c>
       <c r="C66" t="n">
         <v>25.01000022888184</v>
@@ -1897,7 +1897,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>19.95684623718262</v>
+        <v>19.95684242248535</v>
       </c>
       <c r="C67" t="n">
         <v>26</v>
@@ -1926,7 +1926,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.03143882751465</v>
+        <v>21.03144073486328</v>
       </c>
       <c r="C68" t="n">
         <v>27.39999961853027</v>
@@ -1984,7 +1984,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>19.22541999816895</v>
+        <v>19.22542190551758</v>
       </c>
       <c r="C70" t="n">
         <v>24.88999938964844</v>
@@ -2013,7 +2013,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>20.56942558288574</v>
+        <v>20.56942367553711</v>
       </c>
       <c r="C71" t="n">
         <v>26.6299991607666</v>
@@ -2042,7 +2042,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>19.90716934204102</v>
+        <v>19.90716552734375</v>
       </c>
       <c r="C72" t="n">
         <v>25.57999992370605</v>
@@ -2071,7 +2071,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.20289421081543</v>
+        <v>20.20290184020996</v>
       </c>
       <c r="C73" t="n">
         <v>25.95999908447266</v>
@@ -2129,7 +2129,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.86369132995605</v>
+        <v>24.86369323730469</v>
       </c>
       <c r="C75" t="n">
         <v>31.73999977111816</v>
@@ -2158,7 +2158,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>25.27104187011719</v>
+        <v>25.27103614807129</v>
       </c>
       <c r="C76" t="n">
         <v>32.2599983215332</v>
@@ -2187,7 +2187,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>25.08303260803223</v>
+        <v>25.08302688598633</v>
       </c>
       <c r="C77" t="n">
         <v>32.02000045776367</v>
@@ -2216,7 +2216,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.01617813110352</v>
+        <v>23.01617622375488</v>
       </c>
       <c r="C78" t="n">
         <v>29.19000053405762</v>
@@ -2245,7 +2245,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>24.12007522583008</v>
+        <v>24.12007331848145</v>
       </c>
       <c r="C79" t="n">
         <v>30.59000015258789</v>
@@ -2274,7 +2274,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>23.23695182800293</v>
+        <v>23.23695945739746</v>
       </c>
       <c r="C80" t="n">
         <v>29.46999931335449</v>
@@ -2361,7 +2361,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.65273666381836</v>
+        <v>22.65273857116699</v>
       </c>
       <c r="C83" t="n">
         <v>28.54000091552734</v>
@@ -2390,7 +2390,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>21.30241394042969</v>
+        <v>21.30241966247559</v>
       </c>
       <c r="C84" t="n">
         <v>26.6200008392334</v>
@@ -2419,7 +2419,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>21.37443733215332</v>
+        <v>21.37443542480469</v>
       </c>
       <c r="C85" t="n">
         <v>26.70999908447266</v>
@@ -2448,7 +2448,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>21.96662330627441</v>
+        <v>21.96661376953125</v>
       </c>
       <c r="C86" t="n">
         <v>27.45000076293945</v>
@@ -2477,7 +2477,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>22.43088912963867</v>
+        <v>22.43089294433594</v>
       </c>
       <c r="C87" t="n">
         <v>27.79999923706055</v>
@@ -2506,7 +2506,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>23.08445167541504</v>
+        <v>23.08444976806641</v>
       </c>
       <c r="C88" t="n">
         <v>28.61000061035156</v>
@@ -2535,7 +2535,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>26.70728302001953</v>
+        <v>26.70727920532227</v>
       </c>
       <c r="C89" t="n">
         <v>33.09999847412109</v>
@@ -2564,7 +2564,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>28.35710716247559</v>
+        <v>28.35710906982422</v>
       </c>
       <c r="C90" t="n">
         <v>34.90000152587891</v>
@@ -2593,7 +2593,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>28.06458473205566</v>
+        <v>28.06459426879883</v>
       </c>
       <c r="C91" t="n">
         <v>34.54000091552734</v>
@@ -2622,7 +2622,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>25.87077522277832</v>
+        <v>25.87078094482422</v>
       </c>
       <c r="C92" t="n">
         <v>31.84000015258789</v>
@@ -2680,7 +2680,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>27.23135566711426</v>
+        <v>27.23136520385742</v>
       </c>
       <c r="C94" t="n">
         <v>33.27999877929688</v>
@@ -2709,7 +2709,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>28.97422790527344</v>
+        <v>28.97422409057617</v>
       </c>
       <c r="C95" t="n">
         <v>35.40999984741211</v>
@@ -2738,7 +2738,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>31.43649101257324</v>
+        <v>31.43649482727051</v>
       </c>
       <c r="C96" t="n">
         <v>38.13000106811523</v>
@@ -2767,7 +2767,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>30.8428840637207</v>
+        <v>30.84287452697754</v>
       </c>
       <c r="C97" t="n">
         <v>37.40999984741211</v>
@@ -2796,7 +2796,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>31.19741249084473</v>
+        <v>31.19740104675293</v>
       </c>
       <c r="C98" t="n">
         <v>37.84000015258789</v>
@@ -2825,7 +2825,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>31.82174301147461</v>
+        <v>31.82173919677734</v>
       </c>
       <c r="C99" t="n">
         <v>38.31000137329102</v>
@@ -2854,7 +2854,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>34.04784393310547</v>
+        <v>34.0478401184082</v>
       </c>
       <c r="C100" t="n">
         <v>40.9900016784668</v>
@@ -2883,7 +2883,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>33.55776214599609</v>
+        <v>33.55776977539062</v>
       </c>
       <c r="C101" t="n">
         <v>40.40000152587891</v>
@@ -2912,7 +2912,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>34.24621963500977</v>
+        <v>34.24621200561523</v>
       </c>
       <c r="C102" t="n">
         <v>40.93999862670898</v>
@@ -2941,7 +2941,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>34.88195037841797</v>
+        <v>34.88195419311523</v>
       </c>
       <c r="C103" t="n">
         <v>41.70000076293945</v>
@@ -2999,7 +2999,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>38.23944473266602</v>
+        <v>38.23944091796875</v>
       </c>
       <c r="C105" t="n">
         <v>45.43000030517578</v>
@@ -3028,7 +3028,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>39.02225494384766</v>
+        <v>39.02226257324219</v>
       </c>
       <c r="C106" t="n">
         <v>46.36000061035156</v>
@@ -3057,7 +3057,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>39.51885604858398</v>
+        <v>39.51886367797852</v>
       </c>
       <c r="C107" t="n">
         <v>46.95000076293945</v>
@@ -3086,7 +3086,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>40.49656295776367</v>
+        <v>40.49655914306641</v>
       </c>
       <c r="C108" t="n">
         <v>47.81000137329102</v>
@@ -3115,7 +3115,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>39.34459686279297</v>
+        <v>39.3445930480957</v>
       </c>
       <c r="C109" t="n">
         <v>46.45000076293945</v>
@@ -3144,7 +3144,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>34.22006225585938</v>
+        <v>34.22005844116211</v>
       </c>
       <c r="C110" t="n">
         <v>40.40000152587891</v>
@@ -3173,7 +3173,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>37.40665435791016</v>
+        <v>37.40663909912109</v>
       </c>
       <c r="C111" t="n">
         <v>43.84999847412109</v>
@@ -3202,7 +3202,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>34.68539428710938</v>
+        <v>34.68539047241211</v>
       </c>
       <c r="C112" t="n">
         <v>40.65999984741211</v>
@@ -3231,7 +3231,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>41.49278259277344</v>
+        <v>41.49280166625977</v>
       </c>
       <c r="C113" t="n">
         <v>48.63999938964844</v>
@@ -3260,7 +3260,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>40.2341423034668</v>
+        <v>40.23414993286133</v>
       </c>
       <c r="C114" t="n">
         <v>46.86000061035156</v>
@@ -3289,7 +3289,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>37.90732955932617</v>
+        <v>37.90733337402344</v>
       </c>
       <c r="C115" t="n">
         <v>44.15000152587891</v>
@@ -3318,7 +3318,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>40.09676361083984</v>
+        <v>40.09678649902344</v>
       </c>
       <c r="C116" t="n">
         <v>46.70000076293945</v>
@@ -3347,7 +3347,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>37.61282348632812</v>
+        <v>37.61281967163086</v>
       </c>
       <c r="C117" t="n">
         <v>43.52000045776367</v>
@@ -3376,7 +3376,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>38.25237274169922</v>
+        <v>38.25236511230469</v>
       </c>
       <c r="C118" t="n">
         <v>44.2599983215332</v>
@@ -3405,7 +3405,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>45.49491500854492</v>
+        <v>45.49491882324219</v>
       </c>
       <c r="C119" t="n">
         <v>52.63999938964844</v>
@@ -3434,7 +3434,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>47.2894172668457</v>
+        <v>47.28942108154297</v>
       </c>
       <c r="C120" t="n">
         <v>54.34999847412109</v>
@@ -3463,7 +3463,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>48.27262496948242</v>
+        <v>48.27261734008789</v>
       </c>
       <c r="C121" t="n">
         <v>55.47999954223633</v>
@@ -3492,7 +3492,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>47.93328857421875</v>
+        <v>47.93329238891602</v>
       </c>
       <c r="C122" t="n">
         <v>55.09000015258789</v>
@@ -3521,7 +3521,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>44.58805847167969</v>
+        <v>44.58805465698242</v>
       </c>
       <c r="C123" t="n">
         <v>50.88000106811523</v>
@@ -3550,7 +3550,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>48.40013885498047</v>
+        <v>48.40012359619141</v>
       </c>
       <c r="C124" t="n">
         <v>55.22999954223633</v>
@@ -3579,7 +3579,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>43.70296096801758</v>
+        <v>43.70296478271484</v>
       </c>
       <c r="C125" t="n">
         <v>49.86999893188477</v>
@@ -3608,7 +3608,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>46.77075958251953</v>
+        <v>46.77076721191406</v>
       </c>
       <c r="C126" t="n">
         <v>53</v>
@@ -3666,7 +3666,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>50.01824188232422</v>
+        <v>50.01823425292969</v>
       </c>
       <c r="C128" t="n">
         <v>56.68000030517578</v>
@@ -3724,7 +3724,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>51.14691543579102</v>
+        <v>51.14690399169922</v>
       </c>
       <c r="C130" t="n">
         <v>57.59999847412109</v>
@@ -3753,7 +3753,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>53.20698547363281</v>
+        <v>53.20700073242188</v>
       </c>
       <c r="C131" t="n">
         <v>59.91999816894531</v>
@@ -3782,7 +3782,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>53.87038803100586</v>
+        <v>53.87038421630859</v>
       </c>
       <c r="C132" t="n">
         <v>60.2599983215332</v>
@@ -3811,7 +3811,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>55.55105209350586</v>
+        <v>55.55104446411133</v>
       </c>
       <c r="C133" t="n">
         <v>62.13999938964844</v>
@@ -3840,7 +3840,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>57.79491424560547</v>
+        <v>57.79490661621094</v>
       </c>
       <c r="C134" t="n">
         <v>64.65000152587891</v>
@@ -3869,7 +3869,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>57.54269790649414</v>
+        <v>57.54270553588867</v>
       </c>
       <c r="C135" t="n">
         <v>63.97999954223633</v>
@@ -3898,7 +3898,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>59.23354339599609</v>
+        <v>59.23353958129883</v>
       </c>
       <c r="C136" t="n">
         <v>65.86000061035156</v>
@@ -3927,7 +3927,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>61.57194137573242</v>
+        <v>61.57195663452148</v>
       </c>
       <c r="C137" t="n">
         <v>68.45999908447266</v>
@@ -3956,7 +3956,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>63.17315292358398</v>
+        <v>63.17311477661133</v>
       </c>
       <c r="C138" t="n">
         <v>69.83999633789062</v>
@@ -3985,7 +3985,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>62.35000228881836</v>
+        <v>62.34999465942383</v>
       </c>
       <c r="C139" t="n">
         <v>68.93000030517578</v>
@@ -4014,7 +4014,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>65.76013946533203</v>
+        <v>65.76011657714844</v>
       </c>
       <c r="C140" t="n">
         <v>72.69999694824219</v>
@@ -4043,7 +4043,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>67.99287414550781</v>
+        <v>67.99288940429688</v>
       </c>
       <c r="C141" t="n">
         <v>74.76999664306641</v>
@@ -4072,7 +4072,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>67.73822784423828</v>
+        <v>67.73822021484375</v>
       </c>
       <c r="C142" t="n">
         <v>74.48999786376953</v>
@@ -4101,7 +4101,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>75.64060211181641</v>
+        <v>75.64058685302734</v>
       </c>
       <c r="C143" t="n">
         <v>83.18000030517578</v>
@@ -4130,7 +4130,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>76.92525482177734</v>
+        <v>76.92521667480469</v>
       </c>
       <c r="C144" t="n">
         <v>84.16999816894531</v>
@@ -4159,7 +4159,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>78.17733001708984</v>
+        <v>78.17731475830078</v>
       </c>
       <c r="C145" t="n">
         <v>85.54000091552734</v>
@@ -4188,7 +4188,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>86.83221435546875</v>
+        <v>86.83222961425781</v>
       </c>
       <c r="C146" t="n">
         <v>95.01000213623047</v>
@@ -4246,7 +4246,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>83.80596160888672</v>
+        <v>83.80593872070312</v>
       </c>
       <c r="C148" t="n">
         <v>91.26999664306641</v>
@@ -4275,7 +4275,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>85.87193298339844</v>
+        <v>85.8719482421875</v>
       </c>
       <c r="C149" t="n">
         <v>93.51999664306641</v>
@@ -4304,7 +4304,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>91.15026092529297</v>
+        <v>91.15024566650391</v>
       </c>
       <c r="C150" t="n">
         <v>98.83999633789062</v>
@@ -4333,7 +4333,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>90.93815612792969</v>
+        <v>90.93816375732422</v>
       </c>
       <c r="C151" t="n">
         <v>98.61000061035156</v>
@@ -4362,7 +4362,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>97.82698822021484</v>
+        <v>97.82697296142578</v>
       </c>
       <c r="C152" t="n">
         <v>106.0800018310547</v>
@@ -4391,7 +4391,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>103.989387512207</v>
+        <v>103.9894027709961</v>
       </c>
       <c r="C153" t="n">
         <v>112.3300018310547</v>
@@ -4420,7 +4420,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>105.8779067993164</v>
+        <v>105.8779373168945</v>
       </c>
       <c r="C154" t="n">
         <v>114.370002746582</v>
@@ -4449,7 +4449,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>98.87923431396484</v>
+        <v>98.87924957275391</v>
       </c>
       <c r="C155" t="n">
         <v>106.8099975585938</v>
@@ -4478,7 +4478,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>103.0997848510742</v>
+        <v>103.0998001098633</v>
       </c>
       <c r="C156" t="n">
         <v>110.8899993896484</v>
@@ -4536,7 +4536,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>97.09361267089844</v>
+        <v>97.09363555908203</v>
       </c>
       <c r="C158" t="n">
         <v>104.4300003051758</v>
@@ -4565,7 +4565,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>104.6045303344727</v>
+        <v>104.6045532226562</v>
       </c>
       <c r="C159" t="n">
         <v>112.0299987792969</v>
@@ -4594,7 +4594,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>110.1228332519531</v>
+        <v>110.1228103637695</v>
       </c>
       <c r="C160" t="n">
         <v>117.9400024414062</v>
@@ -4681,7 +4681,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>125.5440063476562</v>
+        <v>125.5439605712891</v>
       </c>
       <c r="C163" t="n">
         <v>133.9600067138672</v>
@@ -4710,7 +4710,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>127.7088775634766</v>
+        <v>127.7089233398438</v>
       </c>
       <c r="C164" t="n">
         <v>136.2700042724609</v>
@@ -4739,7 +4739,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>129.6292266845703</v>
+        <v>129.6292114257812</v>
       </c>
       <c r="C165" t="n">
         <v>137.8600006103516</v>
@@ -4768,7 +4768,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>130.7293548583984</v>
+        <v>130.7293701171875</v>
       </c>
       <c r="C166" t="n">
         <v>139.0299987792969</v>
@@ -4797,7 +4797,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>134.8102111816406</v>
+        <v>134.8102722167969</v>
       </c>
       <c r="C167" t="n">
         <v>143.3699951171875</v>
@@ -4855,7 +4855,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>148.7892608642578</v>
+        <v>148.7892913818359</v>
       </c>
       <c r="C169" t="n">
         <v>157.6999969482422</v>
@@ -4913,7 +4913,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>153.2732543945312</v>
+        <v>153.2732238769531</v>
       </c>
       <c r="C171" t="n">
         <v>162.0099945068359</v>
@@ -4942,7 +4942,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>149.2051239013672</v>
+        <v>149.2050933837891</v>
       </c>
       <c r="C172" t="n">
         <v>157.7100067138672</v>
@@ -5029,7 +5029,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>193.0714569091797</v>
+        <v>193.0714416503906</v>
       </c>
       <c r="C175" t="n">
         <v>203.5099945068359</v>
@@ -5058,7 +5058,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>194.4945373535156</v>
+        <v>194.4945526123047</v>
       </c>
       <c r="C176" t="n">
         <v>205.0099945068359</v>
@@ -5116,7 +5116,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>200.0240020751953</v>
+        <v>200.0240478515625</v>
       </c>
       <c r="C178" t="n">
         <v>210.3300018310547</v>
@@ -5145,7 +5145,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>192.5491638183594</v>
+        <v>192.5491027832031</v>
       </c>
       <c r="C179" t="n">
         <v>202.4700012207031</v>
@@ -5174,7 +5174,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>204.1137237548828</v>
+        <v>204.1137847900391</v>
       </c>
       <c r="C180" t="n">
         <v>214.0700073242188</v>
@@ -5203,7 +5203,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>212.0753784179688</v>
+        <v>212.0753479003906</v>
       </c>
       <c r="C181" t="n">
         <v>222.4199981689453</v>
@@ -5232,7 +5232,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>221.1716766357422</v>
+        <v>221.1717224121094</v>
       </c>
       <c r="C182" t="n">
         <v>231.9600067138672</v>
@@ -5261,7 +5261,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>222.0824737548828</v>
+        <v>222.0824890136719</v>
       </c>
       <c r="C183" t="n">
         <v>232.3800048828125</v>
@@ -5319,7 +5319,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>241.0050811767578</v>
+        <v>241.0050354003906</v>
       </c>
       <c r="C185" t="n">
         <v>252.1799926757812</v>
@@ -5348,7 +5348,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>239.1668395996094</v>
+        <v>239.1668090820312</v>
       </c>
       <c r="C186" t="n">
         <v>249.6799926757812</v>
@@ -5377,7 +5377,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>259.4933776855469</v>
+        <v>259.4933471679688</v>
       </c>
       <c r="C187" t="n">
         <v>270.8999938964844</v>
@@ -5435,7 +5435,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>289.7224426269531</v>
+        <v>289.7224731445312</v>
       </c>
       <c r="C189" t="n">
         <v>301.8800048828125</v>
@@ -5464,7 +5464,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>270.5663146972656</v>
+        <v>270.5662841796875</v>
       </c>
       <c r="C190" t="n">
         <v>281.9200134277344</v>
@@ -5493,7 +5493,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>318.2647399902344</v>
+        <v>318.2647705078125</v>
       </c>
       <c r="C191" t="n">
         <v>331.6199951171875</v>
@@ -5522,7 +5522,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>317.856689453125</v>
+        <v>317.8567199707031</v>
       </c>
       <c r="C192" t="n">
         <v>330.5899963378906</v>
@@ -5551,7 +5551,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>323.3659973144531</v>
+        <v>323.3660888671875</v>
       </c>
       <c r="C193" t="n">
         <v>336.3200073242188</v>
@@ -5580,7 +5580,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>299.0019836425781</v>
+        <v>299.0020141601562</v>
       </c>
       <c r="C194" t="n">
         <v>310.9800109863281</v>
@@ -5638,7 +5638,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>297.0478210449219</v>
+        <v>297.0478515625</v>
       </c>
       <c r="C196" t="n">
         <v>308.3099975585938</v>
@@ -5667,7 +5667,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>267.3824768066406</v>
+        <v>267.3825378417969</v>
       </c>
       <c r="C197" t="n">
         <v>277.5199890136719</v>
@@ -5696,7 +5696,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>262.5489807128906</v>
+        <v>262.5490417480469</v>
       </c>
       <c r="C198" t="n">
         <v>271.8699951171875</v>
@@ -5725,7 +5725,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>248.0245971679688</v>
+        <v>248.0246276855469</v>
       </c>
       <c r="C199" t="n">
         <v>256.8299865722656</v>
@@ -5754,7 +5754,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>271.1148986816406</v>
+        <v>271.1148376464844</v>
       </c>
       <c r="C200" t="n">
         <v>280.739990234375</v>
@@ -5783,7 +5783,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>253.0414886474609</v>
+        <v>253.0415344238281</v>
       </c>
       <c r="C201" t="n">
         <v>261.4700012207031</v>
@@ -5841,7 +5841,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>224.6473236083984</v>
+        <v>224.6472625732422</v>
       </c>
       <c r="C203" t="n">
         <v>232.1300048828125</v>
@@ -5870,7 +5870,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>247.6114196777344</v>
+        <v>247.6114349365234</v>
       </c>
       <c r="C204" t="n">
         <v>255.1399993896484</v>
@@ -5928,7 +5928,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>240.4977111816406</v>
+        <v>240.4976806640625</v>
       </c>
       <c r="C206" t="n">
         <v>247.8099975585938</v>
@@ -5957,7 +5957,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>242.6664886474609</v>
+        <v>242.66650390625</v>
       </c>
       <c r="C207" t="n">
         <v>249.4199981689453</v>
@@ -5986,7 +5986,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>280.49365234375</v>
+        <v>280.4936828613281</v>
       </c>
       <c r="C208" t="n">
         <v>288.2999877929688</v>
@@ -6015,7 +6015,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>298.9403686523438</v>
+        <v>298.9403381347656</v>
       </c>
       <c r="C209" t="n">
         <v>307.260009765625</v>
@@ -6044,7 +6044,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>320.1967163085938</v>
+        <v>320.1966552734375</v>
       </c>
       <c r="C210" t="n">
         <v>328.3900146484375</v>
@@ -6102,7 +6102,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>327.5387878417969</v>
+        <v>327.5388488769531</v>
       </c>
       <c r="C212" t="n">
         <v>335.9200134277344</v>
@@ -6218,7 +6218,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>370.9898986816406</v>
+        <v>370.9898681640625</v>
       </c>
       <c r="C216" t="n">
         <v>378.9100036621094</v>
@@ -6276,7 +6276,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>389.2696838378906</v>
+        <v>389.2696228027344</v>
       </c>
       <c r="C218" t="n">
         <v>397.5799865722656</v>
@@ -6334,7 +6334,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>412.6877136230469</v>
+        <v>412.6876525878906</v>
       </c>
       <c r="C220" t="n">
         <v>420.7200012207031</v>
@@ -6363,7 +6363,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>381.8969421386719</v>
+        <v>381.89697265625</v>
       </c>
       <c r="C221" t="n">
         <v>389.3299865722656</v>
@@ -6450,7 +6450,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>411.1031799316406</v>
+        <v>411.1031188964844</v>
       </c>
       <c r="C224" t="n">
         <v>418.3500061035156</v>
@@ -6479,7 +6479,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>410.6528930664062</v>
+        <v>410.6529235839844</v>
       </c>
       <c r="C225" t="n">
         <v>417.1400146484375</v>
@@ -6566,7 +6566,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>417.7090148925781</v>
+        <v>417.7090759277344</v>
       </c>
       <c r="C228" t="n">
         <v>423.4599914550781</v>
@@ -6595,7 +6595,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>415.7757263183594</v>
+        <v>415.7756652832031</v>
       </c>
       <c r="C229" t="n">
         <v>421.5</v>
@@ -6624,7 +6624,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>409.4231872558594</v>
+        <v>409.4231567382812</v>
       </c>
       <c r="C230" t="n">
         <v>415.0599975585938</v>
@@ -6711,7 +6711,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>390.673828125</v>
+        <v>390.6738586425781</v>
       </c>
       <c r="C233" t="n">
         <v>395.260009765625</v>
@@ -6740,7 +6740,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>455.8537902832031</v>
+        <v>455.8538208007812</v>
       </c>
       <c r="C234" t="n">
         <v>460.3599853515625</v>
@@ -6769,7 +6769,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>492.5411376953125</v>
+        <v>492.5411987304688</v>
       </c>
       <c r="C235" t="n">
         <v>497.4100036621094</v>
@@ -6798,7 +6798,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>528.2778930664062</v>
+        <v>528.27783203125</v>
       </c>
       <c r="C236" t="n">
         <v>533.5</v>
@@ -6885,7 +6885,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>513.5844116210938</v>
+        <v>513.5843505859375</v>
       </c>
       <c r="C239" t="n">
         <v>517.8099975585938</v>
